--- a/tracking_reefer.xlsx
+++ b/tracking_reefer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EBB46E-3F8D-4C73-A4A0-56ECD66F2B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89F5C56-E3D8-4276-8B2A-A93828F24316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{89694A71-ED8E-4A85-8684-CA3159E0089E}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>K.Thanakorn</t>
   </si>
   <si>
-    <t>E-mail</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>LKB</t>
+  </si>
+  <si>
+    <t>email</t>
   </si>
 </sst>
 </file>
@@ -169,10 +169,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -528,13 +528,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -548,65 +548,65 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tracking_reefer.xlsx
+++ b/tracking_reefer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89F5C56-E3D8-4276-8B2A-A93828F24316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE5C295-360A-43F7-AF0F-D84306A09863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{89694A71-ED8E-4A85-8684-CA3159E0089E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="131">
   <si>
     <t>company</t>
   </si>
@@ -80,24 +80,12 @@
     <t>Kแหม่ม, K.แก้ว</t>
   </si>
   <si>
-    <t>Tel : 086-378-8200</t>
-  </si>
-  <si>
-    <t>Type : 4ล้อ, 6ล้อ</t>
-  </si>
-  <si>
     <t>Whale Trans Company Limited</t>
   </si>
   <si>
     <t>คุณเล็ก</t>
   </si>
   <si>
-    <t>Tel : 086-323-6458</t>
-  </si>
-  <si>
-    <t>Type : 20', 40', Low Bed</t>
-  </si>
-  <si>
     <t>Airport, PAT</t>
   </si>
   <si>
@@ -111,6 +99,339 @@
   </si>
   <si>
     <t>email</t>
+  </si>
+  <si>
+    <t>NPO Transport co.ltd</t>
+  </si>
+  <si>
+    <t>คุณออย (หัวลาก)</t>
+  </si>
+  <si>
+    <t>คุณ โอ๋ (4-6 ล้อ)</t>
+  </si>
+  <si>
+    <t>Tanachote Transport</t>
+  </si>
+  <si>
+    <t>คุณวุฒิ</t>
+  </si>
+  <si>
+    <t>Chittree@npotransport.co.th</t>
+  </si>
+  <si>
+    <t>suphattra@npotransport.co.th</t>
+  </si>
+  <si>
+    <t>TNCtransport@hotmail.com</t>
+  </si>
+  <si>
+    <t>086-378-8200</t>
+  </si>
+  <si>
+    <t>086-323-6458</t>
+  </si>
+  <si>
+    <t>092-250-8885</t>
+  </si>
+  <si>
+    <t>092-273-1234</t>
+  </si>
+  <si>
+    <t>080-091-2901</t>
+  </si>
+  <si>
+    <t>6ล้อ, 20', 40'</t>
+  </si>
+  <si>
+    <t>20', 40', Low Bed</t>
+  </si>
+  <si>
+    <t>4ล้อ, 6ล้อ</t>
+  </si>
+  <si>
+    <t>4ล้อ, 6ล้อ,10ล้อ</t>
+  </si>
+  <si>
+    <t>Amata (Chon)</t>
+  </si>
+  <si>
+    <t>อมตะนคร, Eastern</t>
+  </si>
+  <si>
+    <t>Friendship Transport</t>
+  </si>
+  <si>
+    <t>คุณป๋อง</t>
+  </si>
+  <si>
+    <t>ALL Center Transport</t>
+  </si>
+  <si>
+    <t>คุณแอมป์</t>
+  </si>
+  <si>
+    <t>transport@all-logistics.co.th</t>
+  </si>
+  <si>
+    <t>S&amp;M Service Transport Co., LTD.</t>
+  </si>
+  <si>
+    <t>คุณ ลี่</t>
+  </si>
+  <si>
+    <t>Maritime Synergy</t>
+  </si>
+  <si>
+    <t>K. ออม (ถามราคา)</t>
+  </si>
+  <si>
+    <t>K-Plus</t>
+  </si>
+  <si>
+    <t>K. A</t>
+  </si>
+  <si>
+    <t>ศรีนครินทร์</t>
+  </si>
+  <si>
+    <t>4ล้อ, 6ล้อ, 20', 40'</t>
+  </si>
+  <si>
+    <t>กรุงเทพฯ</t>
+  </si>
+  <si>
+    <t>LCB</t>
+  </si>
+  <si>
+    <t>LKB, LCB</t>
+  </si>
+  <si>
+    <t>4, 6</t>
+  </si>
+  <si>
+    <t>086-328-2466</t>
+  </si>
+  <si>
+    <t>02-079-9888 Ext.1482</t>
+  </si>
+  <si>
+    <t>085-914-1441</t>
+  </si>
+  <si>
+    <t>085-345-8142</t>
+  </si>
+  <si>
+    <t>081-905-8070</t>
+  </si>
+  <si>
+    <t>pong.99@hotmail.com</t>
+  </si>
+  <si>
+    <t>madam1929@gmail.com</t>
+  </si>
+  <si>
+    <t>project@maritimesynergy.com</t>
+  </si>
+  <si>
+    <t>a_kplus@hotmail.com</t>
+  </si>
+  <si>
+    <t>C-Pro Logistics</t>
+  </si>
+  <si>
+    <t>คุณ สมนึก</t>
+  </si>
+  <si>
+    <t>Borneo Logistics</t>
+  </si>
+  <si>
+    <t>คุณมุก,คุณเจ</t>
+  </si>
+  <si>
+    <t>Sethasit Express</t>
+  </si>
+  <si>
+    <t>คุณนิพัทธ์</t>
+  </si>
+  <si>
+    <t>TSB Transport</t>
+  </si>
+  <si>
+    <t>คุณโก๊ะ</t>
+  </si>
+  <si>
+    <t>Wattanakol Transports 2001</t>
+  </si>
+  <si>
+    <t>คุณหนิง</t>
+  </si>
+  <si>
+    <t>somnuk.k@cprologistics.com</t>
+  </si>
+  <si>
+    <t>fwdexport@borneologistics.com</t>
+  </si>
+  <si>
+    <t>setthasitexpress@hotmail.com</t>
+  </si>
+  <si>
+    <t>tsbtrans2017@gmail.com</t>
+  </si>
+  <si>
+    <t>saengrawee@wattanakol2001.com</t>
+  </si>
+  <si>
+    <t>086-888-8642</t>
+  </si>
+  <si>
+    <t>093-515-0434</t>
+  </si>
+  <si>
+    <t>064-169-0666</t>
+  </si>
+  <si>
+    <t>086-308-0825</t>
+  </si>
+  <si>
+    <t>090-969-9177</t>
+  </si>
+  <si>
+    <t>4w, 6w</t>
+  </si>
+  <si>
+    <t>20', 40', Low Bed, Hydraulic Platform</t>
+  </si>
+  <si>
+    <t>ท่าทราย</t>
+  </si>
+  <si>
+    <t>ปู่เจ้าสมิงพราย</t>
+  </si>
+  <si>
+    <t>พรพฤฒิพงศ์ ทรานสปอร์ต</t>
+  </si>
+  <si>
+    <t>คุณสราวุฒิ</t>
+  </si>
+  <si>
+    <t>Tern Logistics (เพชรทรู พลัส)</t>
+  </si>
+  <si>
+    <t>คุณ ไผ่</t>
+  </si>
+  <si>
+    <t>Type : 20', 40', 10W, 6W</t>
+  </si>
+  <si>
+    <t>BT Service</t>
+  </si>
+  <si>
+    <t>คุณอี๊ด</t>
+  </si>
+  <si>
+    <t>คูณทอง โลจิสติกส์</t>
+  </si>
+  <si>
+    <t>คุณมาลี</t>
+  </si>
+  <si>
+    <t>Pattana Jakkol Motor Transport</t>
+  </si>
+  <si>
+    <t>คุณนน</t>
+  </si>
+  <si>
+    <t>M Bright Logistics and Supply</t>
+  </si>
+  <si>
+    <t>คุณ มุก</t>
+  </si>
+  <si>
+    <t>sapsiri.net@gmail.com</t>
+  </si>
+  <si>
+    <t>arisan@bettersystem.co.th</t>
+  </si>
+  <si>
+    <t>malee@koonthong.com</t>
+  </si>
+  <si>
+    <t>chatchanon.t@pm-transport.com</t>
+  </si>
+  <si>
+    <t>mbright.d2288@gmail.com</t>
+  </si>
+  <si>
+    <t>085-086-4511</t>
+  </si>
+  <si>
+    <t>086-212-3417</t>
+  </si>
+  <si>
+    <t>088-969-8868</t>
+  </si>
+  <si>
+    <t>081-949-8518</t>
+  </si>
+  <si>
+    <t>098-529-5481</t>
+  </si>
+  <si>
+    <t>094-284-8890</t>
+  </si>
+  <si>
+    <t>20', 40', Lowbed, Flatbed</t>
+  </si>
+  <si>
+    <t>20', 40', 10W, 6W</t>
+  </si>
+  <si>
+    <t>20', 40', Project Cargo</t>
+  </si>
+  <si>
+    <t>20', 40', 10 พื้นเรียบ</t>
+  </si>
+  <si>
+    <t>Thai Reefer</t>
+  </si>
+  <si>
+    <t>Catering Lines</t>
+  </si>
+  <si>
+    <t>คุณ นิชาภา</t>
+  </si>
+  <si>
+    <t>Dandaroon Logistics (Thailand)</t>
+  </si>
+  <si>
+    <t>คุณ เอฟ</t>
+  </si>
+  <si>
+    <t>malee@thaireefer.co.th</t>
+  </si>
+  <si>
+    <t>Cateringlines@cateringlines.com</t>
+  </si>
+  <si>
+    <t>nutthapol.poolthin@gmail.com</t>
+  </si>
+  <si>
+    <t>081-989-6068</t>
+  </si>
+  <si>
+    <t>081-840-9650</t>
+  </si>
+  <si>
+    <t>081-888-2773</t>
+  </si>
+  <si>
+    <t>20', 40', Reefer</t>
+  </si>
+  <si>
+    <t>4ล้อ, 6ล้อ, 10ล้อ Reefer</t>
+  </si>
+  <si>
+    <t>มหาชัย พระราม2</t>
   </si>
 </sst>
 </file>
@@ -509,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55901E4B-292A-4B19-A0D2-5C7CB6DF5209}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.375" bestFit="1" customWidth="1"/>
@@ -518,6 +839,7 @@
     <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -528,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -568,57 +890,499 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{57A53708-BF38-40F6-A254-E9E2DDDEFA7F}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{C90B0D24-95F2-48BB-B26B-1ECA32273275}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{34023790-E2E0-49A2-B1E0-0B2C5D641CF6}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{6815E884-91DB-4026-843D-C7DDF24A2AA9}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{645C67DD-8436-4984-AE4A-1E79AA7FA1EC}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{DB9A627A-D522-4A65-B009-2808F56E71CF}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{61260985-696E-4141-A562-AED3CB901A57}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{CCD47446-5541-4C81-B13F-B98B2E12AFD4}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{121C0BF7-B7BA-4B27-9F46-320109F649D8}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{96707A0F-1ABD-4E73-96D0-986E8236B6F9}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{61D41D88-D56C-4090-823D-4F58024707D2}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{35FB060E-33CC-40FB-B310-29F3254C070D}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{899970E9-5C4C-424C-9053-A20AC0378220}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{89EC23B0-38F5-4FEC-A7D4-E4E37CCE96E5}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{6FFF3DC5-DA7B-4F26-8872-F3404D12146A}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{9F8071F4-8DAA-48A5-9275-75B29B11901A}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{D12C5CEA-AC9A-4E04-8C30-D910A38B2722}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{89AF8702-FBFE-44BE-849B-FB2FE6CE905D}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{3AAB3C39-A274-4CF5-8684-A95A33BE68C6}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{4DBE1C32-B184-471D-9FEB-3D40595C5581}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{EA27F708-BBE3-43A3-85ED-FDFD88FD643A}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{6C341326-6791-4F54-81A6-90EE29330844}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{2C2782E6-F5F6-4562-9225-92B93744FF0C}"/>
+    <hyperlink ref="C26" r:id="rId24" xr:uid="{74DFC436-C465-4430-9562-AC338853E16F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId4"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId25"/>
 </worksheet>
 </file>
--- a/tracking_reefer.xlsx
+++ b/tracking_reefer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE5C295-360A-43F7-AF0F-D84306A09863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9113B2-BED3-4A7E-BD64-F540155C5290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{89694A71-ED8E-4A85-8684-CA3159E0089E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="131">
   <si>
     <t>company</t>
   </si>
@@ -483,17 +483,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -935,15 +932,17 @@
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -953,8 +952,12 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1351,11 +1354,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{57A53708-BF38-40F6-A254-E9E2DDDEFA7F}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{C90B0D24-95F2-48BB-B26B-1ECA32273275}"/>

--- a/tracking_reefer.xlsx
+++ b/tracking_reefer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9113B2-BED3-4A7E-BD64-F540155C5290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0EC28B-FC6E-4FC0-8C49-E21A26B0A812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{89694A71-ED8E-4A85-8684-CA3159E0089E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="130">
   <si>
     <t>company</t>
   </si>
@@ -318,9 +318,6 @@
   </si>
   <si>
     <t>คุณ ไผ่</t>
-  </si>
-  <si>
-    <t>Type : 20', 40', 10W, 6W</t>
   </si>
   <si>
     <t>BT Service</t>
@@ -827,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55901E4B-292A-4B19-A0D2-5C7CB6DF5209}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.375" bestFit="1" customWidth="1"/>
@@ -1156,7 +1153,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1176,7 +1173,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -1184,19 +1181,19 @@
         <v>90</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -1204,47 +1201,44 @@
         <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
         <v>53</v>
       </c>
-      <c r="H19" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>94</v>
       </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
         <v>96</v>
       </c>
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -1253,98 +1247,98 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
         <v>98</v>
       </c>
-      <c r="B22" t="s">
-        <v>99</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
         <v>100</v>
       </c>
-      <c r="B23" t="s">
-        <v>101</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>117</v>
       </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>125</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>128</v>
-      </c>
-      <c r="F24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" t="s">
-        <v>129</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
         <v>120</v>
       </c>
-      <c r="B26" t="s">
-        <v>121</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>

--- a/tracking_reefer.xlsx
+++ b/tracking_reefer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0EC28B-FC6E-4FC0-8C49-E21A26B0A812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BCB00F-8298-413B-995E-6F1CA377E284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{89694A71-ED8E-4A85-8684-CA3159E0089E}"/>
   </bookViews>
